--- a/Licencias.xlsx
+++ b/Licencias.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juan.melendezm\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juan.melendezm\OneDrive - Claro Cenam\DyF &amp; TD - Buscador OM\tNPS Diario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38C68518-385D-47F2-ACCB-6A1E665AD791}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{38C68518-385D-47F2-ACCB-6A1E665AD791}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{3310251D-CC15-4208-8723-920BDF24F9A9}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6225" xr2:uid="{315E89AC-049D-4CBC-BBA0-977EA9B4CA5F}"/>
   </bookViews>
@@ -467,46 +467,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -530,7 +512,7 @@
           <bgColor rgb="FF5B9BD5"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="medium">
           <color rgb="FFCCCCCC"/>
@@ -559,8 +541,8 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="medium">
           <color rgb="FFCCCCCC"/>
         </left>
@@ -573,8 +555,6 @@
         <bottom style="medium">
           <color rgb="FF000000"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -594,8 +574,8 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="medium">
           <color rgb="FFCCCCCC"/>
         </left>
@@ -608,8 +588,6 @@
         <bottom style="medium">
           <color rgb="FF000000"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -629,8 +607,8 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="medium">
           <color rgb="FF000000"/>
         </left>
@@ -643,8 +621,6 @@
         <bottom style="medium">
           <color rgb="FF000000"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -656,6 +632,9 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <top style="medium">
+          <color rgb="FF9BC2E6"/>
+        </top>
         <bottom style="medium">
           <color rgb="FF000000"/>
         </bottom>
@@ -663,9 +642,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <top style="medium">
-          <color rgb="FF9BC2E6"/>
-        </top>
         <bottom style="medium">
           <color rgb="FF000000"/>
         </bottom>
@@ -685,12 +661,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8EB08BF9-3CAF-4F8A-B7BA-1AB6EAF2E4E2}" name="Tabla1" displayName="Tabla1" ref="A1:C82" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="5" tableBorderDxfId="6" totalsRowBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8EB08BF9-3CAF-4F8A-B7BA-1AB6EAF2E4E2}" name="Tabla1" displayName="Tabla1" ref="A1:C82" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <autoFilter ref="A1:C82" xr:uid="{1EB77753-C704-4B73-9D4A-390072FC9037}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{7BD220EC-FC0A-4480-8D39-25DB09CE0C75}" name="Operador" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{CA71B84D-567B-4CB2-ADA9-AE9685B5C54E}" name="Supervisor" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{1C9A57D3-78C9-4BFA-9994-DD0755FDF140}" name="Sitio" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{7BD220EC-FC0A-4480-8D39-25DB09CE0C75}" name="Operador" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{CA71B84D-567B-4CB2-ADA9-AE9685B5C54E}" name="Supervisor" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{1C9A57D3-78C9-4BFA-9994-DD0755FDF140}" name="Sitio" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -996,891 +972,893 @@
   <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" customWidth="1"/>
+    <col min="1" max="1" width="26.42578125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" style="4" customWidth="1"/>
+    <col min="4" max="16384" width="11.42578125" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="45.75" thickBot="1">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="30.75" thickBot="1">
-      <c r="A3" s="3" t="s">
+      <c r="C2" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A4" s="3" t="s">
+      <c r="C3" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A5" s="3" t="s">
+      <c r="C4" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A6" s="3" t="s">
+      <c r="C5" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A7" s="3" t="s">
+      <c r="C6" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A8" s="3" t="s">
+      <c r="C7" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A9" s="3" t="s">
+      <c r="C8" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A10" s="3" t="s">
+      <c r="C9" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="30.75" thickBot="1">
-      <c r="A11" s="1" t="s">
+      <c r="C10" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A12" s="3" t="s">
+      <c r="C11" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A13" s="3" t="s">
+      <c r="C12" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A13" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A14" s="3" t="s">
+      <c r="C13" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A15" s="3" t="s">
+      <c r="C14" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A15" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="30.75" thickBot="1">
-      <c r="A16" s="3" t="s">
+      <c r="C15" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A17" s="3" t="s">
+      <c r="C16" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A17" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A18" s="3" t="s">
+      <c r="C17" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A18" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="45.75" thickBot="1">
-      <c r="A19" s="1" t="s">
+      <c r="C18" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A19" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="45.75" thickBot="1">
-      <c r="A20" s="1" t="s">
+      <c r="C19" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A20" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A21" s="3" t="s">
+      <c r="C20" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A21" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="45.75" thickBot="1">
-      <c r="A22" s="1" t="s">
+      <c r="C21" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A22" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="45.75" thickBot="1">
-      <c r="A23" s="1" t="s">
+      <c r="C22" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A23" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A24" s="3" t="s">
+      <c r="C23" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A24" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="45.75" thickBot="1">
-      <c r="A25" s="1" t="s">
+      <c r="C24" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A25" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A26" s="3" t="s">
+      <c r="C25" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A26" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A27" s="3" t="s">
+      <c r="C26" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A27" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="45.75" thickBot="1">
-      <c r="A28" s="1" t="s">
+      <c r="C27" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A28" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="30.75" thickBot="1">
-      <c r="A29" s="1" t="s">
+      <c r="C28" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A29" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="45.75" thickBot="1">
-      <c r="A30" s="1" t="s">
+      <c r="C29" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A30" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="30.75" thickBot="1">
-      <c r="A31" s="3" t="s">
+      <c r="C30" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A31" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="30.75" thickBot="1">
-      <c r="A32" s="1" t="s">
+      <c r="C31" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A33" s="3" t="s">
+    <row r="33" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A33" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A34" s="3" t="s">
+    <row r="34" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A34" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="45.75" thickBot="1">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A35" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A36" s="3" t="s">
+    <row r="36" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A36" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="45.75" thickBot="1">
-      <c r="A37" s="1" t="s">
+    <row r="37" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A37" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="30.75" thickBot="1">
-      <c r="A38" s="3" t="s">
+      <c r="C37" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A38" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A39" s="3" t="s">
+      <c r="C38" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A39" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A40" s="3" t="s">
+      <c r="C39" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A40" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A41" s="3" t="s">
+      <c r="C40" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A41" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="30.75" thickBot="1">
-      <c r="A42" s="3" t="s">
+      <c r="C41" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A42" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A43" s="3" t="s">
+      <c r="C42" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A43" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A44" s="3" t="s">
+      <c r="C43" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A44" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="30.75" thickBot="1">
-      <c r="A45" s="3" t="s">
+      <c r="C44" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A45" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A46" s="3" t="s">
+      <c r="C45" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A46" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A47" s="3" t="s">
+    <row r="47" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A47" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A48" s="3" t="s">
+    <row r="48" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A48" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A49" s="3" t="s">
+    <row r="49" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A49" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A50" s="3" t="s">
+      <c r="C49" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A50" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A51" s="3" t="s">
+      <c r="C50" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A51" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="30.75" thickBot="1">
-      <c r="A52" s="3" t="s">
+      <c r="C51" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A52" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="45.75" thickBot="1">
-      <c r="A53" s="1" t="s">
+      <c r="C52" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A53" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A54" s="3" t="s">
+      <c r="C53" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A54" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="45.75" thickBot="1">
-      <c r="A55" s="1" t="s">
+      <c r="C54" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A55" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="45.75" thickBot="1">
-      <c r="A56" s="1" t="s">
+      <c r="C55" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A56" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A57" s="3" t="s">
+      <c r="C56" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A57" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="45.75" thickBot="1">
-      <c r="A58" s="1" t="s">
+      <c r="C57" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A58" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="30.75" thickBot="1">
-      <c r="A59" s="1" t="s">
+      <c r="C58" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A59" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A60" s="4" t="s">
+      <c r="C59" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A60" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A61" s="3" t="s">
+      <c r="C60" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A61" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="45.75" thickBot="1">
-      <c r="A62" s="1" t="s">
+      <c r="C61" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A62" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="30.75" thickBot="1">
-      <c r="A63" s="1" t="s">
+    <row r="63" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A63" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="45.75" thickBot="1">
-      <c r="A64" s="1" t="s">
+    <row r="64" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A64" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="45.75" thickBot="1">
-      <c r="A65" s="1" t="s">
+    <row r="65" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A65" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A66" s="3" t="s">
+    <row r="66" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A66" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="45.75" thickBot="1">
-      <c r="A67" s="1" t="s">
+    <row r="67" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A67" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="45.75" thickBot="1">
-      <c r="A68" s="1" t="s">
+    <row r="68" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A68" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="45.75" thickBot="1">
-      <c r="A69" s="1" t="s">
+    <row r="69" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A69" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="45.75" thickBot="1">
-      <c r="A70" s="1" t="s">
+    <row r="70" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A70" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="45.75" thickBot="1">
-      <c r="A71" s="1" t="s">
+    <row r="71" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A71" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="44.25" thickBot="1">
-      <c r="A72" s="3" t="s">
+    <row r="72" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A72" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="27" thickBot="1">
-      <c r="A73" s="5" t="s">
+    <row r="73" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A73" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B73" s="6" t="s">
+      <c r="B73" s="10"/>
+      <c r="C73" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C73" s="6"/>
-    </row>
-    <row r="74" spans="1:3" ht="27" thickBot="1">
-      <c r="A74" s="5" t="s">
+    </row>
+    <row r="74" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A74" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="10"/>
+      <c r="C74" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C74" s="6"/>
-    </row>
-    <row r="75" spans="1:3" ht="39.75" thickBot="1">
-      <c r="A75" s="5" t="s">
+    </row>
+    <row r="75" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A75" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B75" s="6" t="s">
+      <c r="B75" s="10"/>
+      <c r="C75" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C75" s="6"/>
-    </row>
-    <row r="76" spans="1:3" ht="27" thickBot="1">
-      <c r="A76" s="5" t="s">
+    </row>
+    <row r="76" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A76" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B76" s="6" t="s">
+      <c r="B76" s="10"/>
+      <c r="C76" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C76" s="6"/>
-    </row>
-    <row r="77" spans="1:3" ht="39.75" thickBot="1">
-      <c r="A77" s="5" t="s">
+    </row>
+    <row r="77" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A77" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="10"/>
+      <c r="C77" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C77" s="6"/>
-    </row>
-    <row r="78" spans="1:3" ht="27" thickBot="1">
-      <c r="A78" s="5" t="s">
+    </row>
+    <row r="78" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A78" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="10"/>
+      <c r="C78" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C78" s="6"/>
-    </row>
-    <row r="79" spans="1:3" ht="27" thickBot="1">
-      <c r="A79" s="5" t="s">
+    </row>
+    <row r="79" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A79" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="B79" s="6" t="s">
+      <c r="B79" s="10"/>
+      <c r="C79" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C79" s="6"/>
-    </row>
-    <row r="80" spans="1:3" ht="39.75" thickBot="1">
-      <c r="A80" s="5" t="s">
+    </row>
+    <row r="80" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A80" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B80" s="6" t="s">
+      <c r="B80" s="10"/>
+      <c r="C80" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C80" s="6"/>
-    </row>
-    <row r="81" spans="1:3" ht="27" thickBot="1">
-      <c r="A81" s="5" t="s">
+    </row>
+    <row r="81" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A81" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B81" s="6" t="s">
+      <c r="B81" s="10"/>
+      <c r="C81" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C81" s="6"/>
-    </row>
-    <row r="82" spans="1:3" ht="26.25">
-      <c r="A82" s="10" t="s">
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="B82" s="11" t="s">
+      <c r="B82" s="12"/>
+      <c r="C82" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="C82" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2030,6 +2008,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -2038,20 +2022,44 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{499146DB-7450-4136-823E-A20977BC98D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{499146DB-7450-4136-823E-A20977BC98D1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="500d996f-f1f4-4aa2-9056-76b25a0746a4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C889B942-4E8E-45E8-893E-82EC9F551C9E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A2F003A-00AA-4592-A68B-47C8E5C543EF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="500d996f-f1f4-4aa2-9056-76b25a0746a4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A2F003A-00AA-4592-A68B-47C8E5C543EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C889B942-4E8E-45E8-893E-82EC9F551C9E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>